--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484690_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484690_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1329</v>
+        <v>11.6032</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5587</v>
+        <v>12.8061</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4259</v>
+        <v>-1.2029</v>
       </c>
       <c r="G2" t="n">
         <v>10.3071</v>
@@ -610,13 +610,13 @@
         <v>0.9163</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8596</v>
+        <v>-0.3893</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5694</v>
+        <v>-0.322</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2903</v>
+        <v>-0.0673</v>
       </c>
       <c r="V2" t="n">
         <v>1.3189</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7938</v>
+        <v>7.1917</v>
       </c>
       <c r="E3" t="n">
-        <v>5.924</v>
+        <v>5.5945</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8697</v>
+        <v>1.5972</v>
       </c>
       <c r="G3" t="n">
         <v>1.2262</v>
@@ -688,13 +688,13 @@
         <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8168</v>
+        <v>1.2147</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5837</v>
+        <v>0.2542</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2331</v>
+        <v>0.9606</v>
       </c>
       <c r="V3" t="n">
         <v>2.9182</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4251</v>
+        <v>1.5842</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7958</v>
+        <v>1.0934</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2209</v>
+        <v>0.4908</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4003</v>
+        <v>1.6247</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8103</v>
+        <v>0.5253</v>
       </c>
       <c r="I4" t="n">
-        <v>1.59</v>
+        <v>1.0994</v>
       </c>
       <c r="J4" t="n">
-        <v>1.395</v>
+        <v>1.3136</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0992</v>
+        <v>0.0217</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4942</v>
+        <v>1.2919</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0053</v>
+        <v>0.3112</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9095</v>
+        <v>0.5036</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0958</v>
+        <v>-0.1925</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.8326</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2986</v>
+        <v>-0.1833</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4731</v>
+        <v>0.1427</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7858000000000001</v>
+        <v>-0.0369</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6872</v>
+        <v>0.1797</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3843</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.609</v>
+        <v>1.3338</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0934</v>
+        <v>-1.565</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5155999999999999</v>
+        <v>2.8988</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6247</v>
+        <v>2.4003</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5253</v>
+        <v>0.8103</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0994</v>
+        <v>1.59</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3136</v>
+        <v>1.395</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0217</v>
+        <v>-0.0992</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2919</v>
+        <v>1.4942</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3112</v>
+        <v>1.0053</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5036</v>
+        <v>0.9095</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1925</v>
+        <v>0.0958</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1833</v>
+        <v>-3.2986</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1675</v>
+        <v>0.3818</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0369</v>
+        <v>0.0166</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2044</v>
+        <v>0.3652</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3843</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ABAD MOLINER</t>
+          <t>P. ARISTA CALLAU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3241</v>
+        <v>0.6312</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1101</v>
+        <v>1.2221</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4342</v>
+        <v>-0.5909</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3846</v>
+        <v>1.8346</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2564</v>
+        <v>1.3794</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1282</v>
+        <v>0.4552</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.0823</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.5047</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.5776</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3846</v>
+        <v>-1.2477</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2564</v>
+        <v>-0.1253</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1282</v>
+        <v>-1.1223</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-3.1154</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.2149</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0606</v>
+        <v>-0.0404</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1101</v>
+        <v>-0.5011</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0495</v>
+        <v>0.4608</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.9524</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.9035</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ARISTA CALLAU</t>
+          <t>M. ABAD MOLINER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2877</v>
+        <v>0.3984</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8786</v>
+        <v>-0.1101</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5909</v>
+        <v>0.5085</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8346</v>
+        <v>0.3846</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3794</v>
+        <v>0.2564</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4552</v>
+        <v>0.1282</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0823</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5047</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5776</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2477</v>
+        <v>0.3846</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1253</v>
+        <v>0.2564</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1223</v>
+        <v>0.1282</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.1154</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.2149</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3839</v>
+        <v>0.0138</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8446</v>
+        <v>-0.1101</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4608</v>
+        <v>0.1239</v>
       </c>
       <c r="V8" t="n">
-        <v>1.9524</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.708</v>
+        <v>-0.0013</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5324</v>
+        <v>-2.1478</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8245</v>
+        <v>2.1465</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4566</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5183</v>
+        <v>0.1883</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3492</v>
+        <v>0.0355</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1692</v>
+        <v>0.1529</v>
       </c>
       <c r="V9" t="n">
         <v>1.267</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>M. PERAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2281</v>
+        <v>-0.746</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0747</v>
+        <v>-1.3916</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1535</v>
+        <v>0.6456</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1747</v>
+        <v>-2.3297</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2354</v>
+        <v>0.5617</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0608</v>
+        <v>-2.8914</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.092</v>
+        <v>-0.3358</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.217</v>
+        <v>1.9783</v>
       </c>
       <c r="L10" t="n">
-        <v>0.125</v>
+        <v>-2.3141</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0827</v>
+        <v>-1.994</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0184</v>
+        <v>-1.4166</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0643</v>
+        <v>-0.5774</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2367</v>
+        <v>0.7885</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2006</v>
+        <v>0.0438</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4373</v>
+        <v>0.7447</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.0623</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PERAL</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2293</v>
+        <v>-1.2936</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0235</v>
+        <v>-1.3631</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7942</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3297</v>
+        <v>-1.1747</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5617</v>
+        <v>-1.2354</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8914</v>
+        <v>0.0608</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3358</v>
+        <v>-1.092</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9783</v>
+        <v>-1.217</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.3141</v>
+        <v>0.125</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.994</v>
+        <v>-0.0827</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4166</v>
+        <v>-0.0184</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5774</v>
+        <v>-0.0643</v>
       </c>
       <c r="P11" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3051</v>
+        <v>-0.3022</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.0878</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8933</v>
+        <v>-0.2144</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0623</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5811</v>
+        <v>-1.5068</v>
       </c>
       <c r="E12" t="n">
         <v>-2.0152</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4342</v>
+        <v>0.5085</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8974</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0606</v>
+        <v>0.0138</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0495</v>
+        <v>0.1239</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6231</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1154</v>
+        <v>-5.209</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.998</v>
+        <v>-6.9429</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8826</v>
+        <v>1.734</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0218</v>
@@ -1468,13 +1468,13 @@
         <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>0.103</v>
+        <v>0.0094</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2586</v>
+        <v>-0.2036</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3617</v>
+        <v>0.213</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5473</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.986</v>
+        <v>15.2611</v>
       </c>
       <c r="E14" t="n">
-        <v>6.180299999999998</v>
+        <v>6.455700000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>8.805599999999998</v>
+        <v>8.8056</v>
       </c>
       <c r="G14" t="n">
-        <v>11.1726</v>
+        <v>11.17260000000001</v>
       </c>
       <c r="H14" t="n">
         <v>5.082299999999999</v>
@@ -1522,7 +1522,7 @@
         <v>15.7405</v>
       </c>
       <c r="K14" t="n">
-        <v>7.083</v>
+        <v>7.083000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>8.6576</v>
@@ -1546,13 +1546,13 @@
         <v>10.9954</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7458</v>
+        <v>2.021099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.297</v>
+        <v>-1.0215</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0427</v>
+        <v>3.043</v>
       </c>
       <c r="V14" t="n">
         <v>5.732699999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1029</v>
+        <v>0.9357</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1868</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0838</v>
+        <v>0.1217</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0466</v>
+        <v>1.5434</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6428</v>
+        <v>0.1554</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.5962</v>
+        <v>1.388</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1015</v>
+        <v>1.7129</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2229</v>
+        <v>0.421</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1214</v>
+        <v>1.2919</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0549</v>
+        <v>-0.1695</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.2656</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4748</v>
+        <v>0.0961</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4462</v>
+        <v>0.0362</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0853</v>
+        <v>0.0174</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3609</v>
+        <v>0.0188</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.2224</v>
+        <v>-0.6439</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.2224</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>J. TALLON GUIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4229</v>
+        <v>0.9074</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4294</v>
+        <v>0.4179</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0065</v>
+        <v>0.4895</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5434</v>
+        <v>-0.8018</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1554</v>
+        <v>-1.1737</v>
       </c>
       <c r="I16" t="n">
-        <v>1.388</v>
+        <v>0.3719</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7129</v>
+        <v>1.2059</v>
       </c>
       <c r="K16" t="n">
-        <v>0.421</v>
+        <v>-0.2883</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2919</v>
+        <v>1.4942</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1695</v>
+        <v>-2.0077</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2656</v>
+        <v>-0.8854</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0961</v>
+        <v>-1.1223</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9163</v>
+        <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4766</v>
+        <v>0.2144</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3673</v>
+        <v>-0.2224</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1094</v>
+        <v>0.4368</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6439</v>
+        <v>0.945</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BALFAGON SULLER</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3523</v>
+        <v>0.4799</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6954</v>
+        <v>2.456</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3431</v>
+        <v>-1.9761</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9791</v>
+        <v>0.0466</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1105</v>
+        <v>2.6428</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1314</v>
+        <v>-2.5962</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5302</v>
+        <v>2.1015</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2387</v>
+        <v>3.2229</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7085</v>
+        <v>-1.1214</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4489</v>
+        <v>-2.0549</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1282</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-1.4748</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0771</v>
+        <v>0.8232</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1652</v>
+        <v>0.3545</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2422</v>
+        <v>0.4687</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. TALLON GUIA</t>
+          <t>M. BALFAGON SULLER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3617</v>
+        <v>-0.3057</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3514</v>
+        <v>-0.5992</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0103</v>
+        <v>0.2936</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8018</v>
+        <v>-0.9791</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1737</v>
+        <v>-1.1105</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3719</v>
+        <v>0.1314</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2059</v>
+        <v>-0.5302</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2883</v>
+        <v>-1.2387</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4942</v>
+        <v>0.7085</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0077</v>
+        <v>-0.4489</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8854</v>
+        <v>0.1282</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1223</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="P18" t="n">
         <v>0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3823</v>
+        <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0547</v>
+        <v>0.1237</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9917</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.063</v>
+        <v>0.1927</v>
       </c>
       <c r="V18" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5818</v>
+        <v>-0.6945</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1599</v>
+        <v>-1.583</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5782</v>
+        <v>0.8885</v>
       </c>
       <c r="G19" t="n">
         <v>0.3025</v>
@@ -1936,13 +1936,13 @@
         <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2403</v>
+        <v>-0.3531</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4683</v>
+        <v>-0.8914</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2279</v>
+        <v>0.5382</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6439</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7397</v>
+        <v>-1.5619</v>
       </c>
       <c r="E20" t="n">
         <v>-2.5724</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8327</v>
+        <v>1.0105</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6228</v>
@@ -2014,13 +2014,13 @@
         <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0228</v>
+        <v>0.155</v>
       </c>
       <c r="T20" t="n">
         <v>0.0536</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.1014</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6439</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4333</v>
+        <v>-2.0217</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2514</v>
+        <v>-2.6917</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1819</v>
+        <v>0.67</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3096</v>
+        <v>-0.3492</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.742</v>
+        <v>1.6127</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5675</v>
+        <v>-1.9619</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1691</v>
+        <v>1.8188</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2108</v>
+        <v>2.2417</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0417</v>
+        <v>-0.4228</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1404</v>
+        <v>-2.168</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5312</v>
+        <v>-0.629</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6092</v>
+        <v>-1.5391</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5498</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7181</v>
+        <v>-0.0232</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.8454</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0526</v>
+        <v>0.8222</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4398</v>
+        <v>-2.1507</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0763</v>
+        <v>-1.1552</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6365</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3492</v>
+        <v>-1.3096</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6127</v>
+        <v>-0.742</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9619</v>
+        <v>-0.5675</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8188</v>
+        <v>-0.1691</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2417</v>
+        <v>-0.2108</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4228</v>
+        <v>0.0417</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.168</v>
+        <v>-1.1404</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.629</v>
+        <v>-0.5312</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5391</v>
+        <v>-0.6092</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4413</v>
+        <v>-0.4355</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.23</v>
+        <v>-0.6746</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7887</v>
+        <v>0.2391</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1784</v>
+        <v>-2.431</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3142</v>
+        <v>-1.0257</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8642</v>
+        <v>-1.4053</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5679</v>
@@ -2248,13 +2248,13 @@
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0869</v>
+        <v>-0.3395</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1199</v>
+        <v>-0.8314</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0329</v>
+        <v>0.4919</v>
       </c>
       <c r="V23" t="n">
         <v>0.0104</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4249</v>
+        <v>-5.5793</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3227</v>
+        <v>-3.1881</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1022</v>
+        <v>-2.3912</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4348</v>
@@ -2326,13 +2326,13 @@
         <v>1.6493</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.6173</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9314</v>
+        <v>0.066</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1597</v>
+        <v>0.5513</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5785</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.9861</v>
+        <v>-12.4218</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.127500000000001</v>
+        <v>-9.1274</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.8584</v>
+        <v>-3.2943</v>
       </c>
       <c r="G25" t="n">
         <v>-11.1727</v>
@@ -2404,13 +2404,13 @@
         <v>14.6607</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.745699999999999</v>
+        <v>0.8184999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.0428</v>
+        <v>-3.0427</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2968</v>
+        <v>3.8611</v>
       </c>
       <c r="V25" t="n">
         <v>-5.732600000000001</v>
@@ -2419,7 +2419,7 @@
         <v>0.3427999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.075299999999999</v>
+        <v>-6.0753</v>
       </c>
     </row>
   </sheetData>
